--- a/stations.xlsx
+++ b/stations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\river-monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927FF9D7-6FCB-4CFA-AFCF-24982762B570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E6B11D-7C02-435F-8C59-1FA8B274041E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{EC9B290A-547C-42C4-9CD1-474BB88691F8}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="552">
   <si>
     <t>管轄者名</t>
     <rPh sb="0" eb="2">
@@ -1914,6 +1914,390 @@
   </si>
   <si>
     <t>river_kana</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奈良市荻町</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）奈良市西部</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ナラシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）奈良市東部</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ナラシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）奈良市東部</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ナラシトウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）大和郡山市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ヤマトコオリヤマシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）天理市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北東部）山添村</t>
+    <rPh sb="1" eb="4">
+      <t>ホクトウブ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤマゾエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）生駒市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イコマシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）平群町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘグリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>チョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）三郷町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>サンゴウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）斑鳩町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イカルガチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）大和高田市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ヤマトタカダシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）御所市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゴセシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）香芝市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カシバシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）王寺町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>オウジチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）広陵町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>コウリョウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）河合町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カワイチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）橿原市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カシハラシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）桜井市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>サクライシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）川西町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カワニシチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）三宅町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ミヤケチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）田原本町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>タワラモトチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）高取町</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>タカトリチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北西部）明日香村</t>
+    <rPh sb="1" eb="4">
+      <t>ホクセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>アスカムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（北東部）宇陀市</t>
+    <rPh sb="1" eb="4">
+      <t>ホクトウブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ウダシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（南東部）曽爾村</t>
+    <rPh sb="1" eb="4">
+      <t>ナントウブ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソニ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（南東部）東吉野村</t>
+    <rPh sb="1" eb="4">
+      <t>ナントウブ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ヒガシヨシノムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（五條・北部吉野）吉野町</t>
+    <rPh sb="1" eb="3">
+      <t>ゴジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ホクブヨシノ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ヨシノチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（五條・北部吉野）大淀町</t>
+    <rPh sb="1" eb="3">
+      <t>ゴジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ホクブヨシノ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>オオヨドチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（五條・北部吉野）下市町</t>
+    <rPh sb="1" eb="3">
+      <t>ゴジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ホクブヨシノ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シモイチ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>チョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（南東部）天川村</t>
+    <rPh sb="1" eb="4">
+      <t>ナントウブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>テンカワムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（南東部）川上村</t>
+    <rPh sb="1" eb="4">
+      <t>ナントウブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カワカミムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（五條・北部吉野）五條市北部</t>
+    <rPh sb="1" eb="3">
+      <t>ゴジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ホクブヨシノ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ゴジョウシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ホクブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（南西部）五條市南部</t>
+    <rPh sb="1" eb="4">
+      <t>ナンセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゴジョウシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナンブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（南西部）十津川村</t>
+  </si>
+  <si>
+    <t>（南西部）十津川村</t>
+    <rPh sb="1" eb="4">
+      <t>ナンセイブ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>トツカワムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>region</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5172,7 +5556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA24947-9F62-4ED7-9186-451FA9173714}">
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
@@ -5183,11 +5567,12 @@
     <col min="6" max="6" width="10.75" customWidth="1"/>
     <col min="7" max="7" width="23.9140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>372</v>
       </c>
@@ -5213,37 +5598,40 @@
         <v>377</v>
       </c>
       <c r="I1" t="s">
+        <v>551</v>
+      </c>
+      <c r="J1" t="s">
         <v>383</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>384</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>464</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>465</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>466</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>467</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>462</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>463</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>460</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5268,40 +5656,43 @@
       <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J2" s="1">
         <v>34.689166700000001</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>135.82749999999999</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="Q2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(O2,"ofcCd="),"&amp;")</f>
+      <c r="R2" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(P2,"ofcCd="),"&amp;")</f>
         <v>7425</v>
       </c>
-      <c r="R2" t="str">
-        <f>_xlfn.TEXTAFTER(O2,"obsCd=")</f>
+      <c r="S2" t="str">
+        <f>_xlfn.TEXTAFTER(P2,"obsCd=")</f>
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -5326,40 +5717,43 @@
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J3" s="1">
         <v>34.704444000000002</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>135.78</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q64" si="0">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(O3,"ofcCd="),"&amp;")</f>
+      <c r="R3" t="str">
+        <f t="shared" ref="R3:R64" si="0">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(P3,"ofcCd="),"&amp;")</f>
         <v>7425</v>
       </c>
-      <c r="R3" t="str">
-        <f t="shared" ref="R3:R64" si="1">_xlfn.TEXTAFTER(O3,"obsCd=")</f>
+      <c r="S3" t="str">
+        <f t="shared" ref="S3:S64" si="1">_xlfn.TEXTAFTER(P3,"obsCd=")</f>
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -5384,40 +5778,43 @@
       <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J4" s="1">
         <v>34.662500000000001</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>135.80138890000001</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="R4" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
         <f t="shared" si="1"/>
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5442,37 +5839,40 @@
       <c r="H5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J5" s="1">
         <v>34.666388900000001</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>135.8230556</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="R5" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
         <f t="shared" si="1"/>
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5497,40 +5897,43 @@
       <c r="H6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J6" s="1">
         <v>34.649166700000002</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>135.82749999999999</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>37</v>
       </c>
       <c r="N6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="P6" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R6" t="str">
+      <c r="S6" t="str">
         <f t="shared" si="1"/>
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2">
         <v>156</v>
       </c>
@@ -5553,31 +5956,34 @@
         <v>39</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="1">
+        <v>515</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="J7" s="1">
         <v>34.643333300000002</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>135.96916669999999</v>
       </c>
-      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="1"/>
+      <c r="P7" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="R7" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R7" t="str">
+      <c r="S7" t="str">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2">
         <v>158</v>
       </c>
@@ -5602,29 +6008,32 @@
       <c r="H8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J8" s="1">
         <v>34.735277799999999</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>135.96805560000001</v>
       </c>
-      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="1"/>
+      <c r="P8" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="R8" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R8" t="str">
+      <c r="S8" t="str">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2">
         <v>29</v>
       </c>
@@ -5649,40 +6058,43 @@
       <c r="H9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="J9" s="1">
         <v>34.619166700000001</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>135.80138890000001</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="P9" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="Q9" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="R9" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R9" t="str">
+      <c r="S9" t="str">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -5707,40 +6119,43 @@
       <c r="H10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J10" s="1">
         <v>34.597222199999997</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>135.83611110000001</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="P10" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="Q10" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="R10" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R10" t="str">
+      <c r="S10" t="str">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -5765,32 +6180,35 @@
       <c r="H11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J11" s="1">
         <v>34.596388900000001</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>135.8713889</v>
       </c>
-      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="1"/>
+      <c r="P11" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="R11" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R11" t="str">
+      <c r="S11" t="str">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2">
         <v>154</v>
       </c>
@@ -5815,29 +6233,32 @@
       <c r="H12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="J12" s="1">
         <v>34.647222200000002</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>136.06194439999999</v>
       </c>
-      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="1"/>
+      <c r="P12" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="R12" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R12" t="str">
+      <c r="S12" t="str">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2">
         <v>157</v>
       </c>
@@ -5862,29 +6283,32 @@
       <c r="H13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="J13" s="1">
         <v>34.675555600000003</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>135.97388889999999</v>
       </c>
-      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="1"/>
+      <c r="P13" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="R13" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2">
         <v>23</v>
       </c>
@@ -5909,37 +6333,40 @@
       <c r="H14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J14" s="1">
         <v>34.662222200000002</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>135.7622222</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>66</v>
       </c>
       <c r="N14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="P14" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="R14" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R14" t="str">
+      <c r="S14" t="str">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2">
         <v>25</v>
       </c>
@@ -5964,40 +6391,43 @@
       <c r="H15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="J15" s="1">
         <v>34.647222200000002</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>135.80138890000001</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>53</v>
       </c>
       <c r="N15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O15" s="5" t="s">
+      <c r="P15" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="P15" s="5" t="s">
+      <c r="Q15" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="R15" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R15" t="str">
+      <c r="S15" t="str">
         <f t="shared" si="1"/>
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2">
         <v>169</v>
       </c>
@@ -6022,40 +6452,43 @@
       <c r="H16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="J16" s="1">
         <v>34.6245361</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>135.79106390000001</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="5" t="s">
+      <c r="P16" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="Q16" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="R16" t="str">
         <f t="shared" si="0"/>
         <v>22069</v>
       </c>
-      <c r="R16" t="str">
+      <c r="S16" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2">
         <v>170</v>
       </c>
@@ -6080,40 +6513,43 @@
       <c r="H17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="J17" s="1">
         <v>34.597680599999997</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>135.7693917</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="O17" s="5" t="s">
+      <c r="P17" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="Q17" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="R17" t="str">
         <f t="shared" si="0"/>
         <v>22069</v>
       </c>
-      <c r="R17" t="str">
+      <c r="S17" t="str">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2">
         <v>21</v>
       </c>
@@ -6138,40 +6574,43 @@
       <c r="H18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J18" s="1">
         <v>34.674999999999997</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>135.7069444</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>67</v>
       </c>
       <c r="N18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="P18" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="P18" s="6" t="s">
+      <c r="Q18" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="R18" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R18" t="str">
+      <c r="S18" t="str">
         <f t="shared" si="1"/>
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2">
         <v>24</v>
       </c>
@@ -6196,37 +6635,40 @@
       <c r="H19" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J19" s="1">
         <v>34.736944399999999</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>135.7222222</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O19" s="5" t="s">
+      <c r="P19" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="Q19" t="str">
+      <c r="R19" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R19" t="str">
+      <c r="S19" t="str">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2">
         <v>27</v>
       </c>
@@ -6251,40 +6693,43 @@
       <c r="H20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J20" s="1">
         <v>34.694722200000001</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>135.70249999999999</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="O20" s="5" t="s">
+      <c r="P20" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="P20" s="5" t="s">
+      <c r="Q20" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="R20" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R20" t="str">
+      <c r="S20" t="str">
         <f t="shared" si="1"/>
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2">
         <v>22</v>
       </c>
@@ -6309,38 +6754,41 @@
       <c r="H21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="J21" s="1">
         <v>34.627222199999999</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>135.7041667</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O21" s="5" t="s">
+      <c r="P21" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="P21" s="4"/>
-      <c r="Q21" t="str">
+      <c r="Q21" s="4"/>
+      <c r="R21" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R21" t="str">
+      <c r="S21" t="str">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2">
         <v>28</v>
       </c>
@@ -6365,32 +6813,35 @@
       <c r="H22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="J22" s="1">
         <v>34.589722199999997</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>135.68833330000001</v>
       </c>
-      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="4" t="s">
+      <c r="O22" s="1"/>
+      <c r="P22" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="Q22" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="R22" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R22" t="str">
+      <c r="S22" t="str">
         <f t="shared" si="1"/>
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2">
         <v>173</v>
       </c>
@@ -6415,36 +6866,39 @@
       <c r="H23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="J23" s="1">
         <v>34.599130600000002</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>135.70888059999999</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="1"/>
+      <c r="P23" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="P23" s="6" t="s">
+      <c r="Q23" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="Q23" t="str">
+      <c r="R23" t="str">
         <f t="shared" si="0"/>
         <v>22069</v>
       </c>
-      <c r="R23" t="str">
+      <c r="S23" t="str">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2">
         <v>26</v>
       </c>
@@ -6469,40 +6923,43 @@
       <c r="H24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J24" s="1">
         <v>34.613055600000003</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>135.74861110000001</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O24" s="5" t="s">
+      <c r="P24" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="P24" s="5" t="s">
+      <c r="Q24" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="Q24" t="str">
+      <c r="R24" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R24" t="str">
+      <c r="S24" t="str">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2">
         <v>41</v>
       </c>
@@ -6527,40 +6984,43 @@
       <c r="H25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="J25" s="1">
         <v>34.523611099999997</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>135.73750000000001</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>101</v>
       </c>
       <c r="N25" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O25" s="5" t="s">
+      <c r="P25" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="P25" s="6" t="s">
+      <c r="Q25" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="Q25" t="str">
+      <c r="R25" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R25" t="str">
+      <c r="S25" t="str">
         <f t="shared" si="1"/>
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2">
         <v>44</v>
       </c>
@@ -6585,37 +7045,40 @@
       <c r="H26" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J26" s="1">
         <v>34.462777799999998</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>135.74055559999999</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>67</v>
       </c>
       <c r="N26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O26" s="5" t="s">
+      <c r="P26" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="R26" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R26" t="str">
+      <c r="S26" t="str">
         <f t="shared" si="1"/>
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2">
         <v>45</v>
       </c>
@@ -6640,37 +7103,40 @@
       <c r="H27" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J27" s="1">
         <v>34.417777800000003</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>135.75</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="M27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="O27" s="5" t="s">
+      <c r="P27" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="R27" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R27" t="str">
+      <c r="S27" t="str">
         <f t="shared" si="1"/>
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2">
         <v>42</v>
       </c>
@@ -6695,40 +7161,43 @@
       <c r="H28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="J28" s="1">
         <v>34.558333300000001</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>135.7055556</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="O28" s="5" t="s">
+      <c r="P28" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="P28" s="5" t="s">
+      <c r="Q28" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="Q28" t="str">
+      <c r="R28" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R28" t="str">
+      <c r="S28" t="str">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2">
         <v>46</v>
       </c>
@@ -6753,40 +7222,43 @@
       <c r="H29" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="J29" s="1">
         <v>34.5380556</v>
       </c>
-      <c r="J29" s="1">
+      <c r="K29" s="1">
         <v>135.71805560000001</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="O29" s="5" t="s">
+      <c r="P29" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="P29" s="6" t="s">
+      <c r="Q29" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="Q29" t="str">
+      <c r="R29" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R29" t="str">
+      <c r="S29" t="str">
         <f t="shared" si="1"/>
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2">
         <v>174</v>
       </c>
@@ -6811,36 +7283,39 @@
       <c r="H30" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="J30" s="1">
         <v>34.585983300000002</v>
       </c>
-      <c r="J30" s="1">
+      <c r="K30" s="1">
         <v>135.68451110000001</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="M30" s="1"/>
       <c r="N30" s="1"/>
-      <c r="O30" s="4" t="s">
+      <c r="O30" s="1"/>
+      <c r="P30" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="P30" s="6" t="s">
+      <c r="Q30" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="R30" t="str">
         <f t="shared" si="0"/>
         <v>22069</v>
       </c>
-      <c r="R30" t="str">
+      <c r="S30" t="str">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2">
         <v>43</v>
       </c>
@@ -6865,37 +7340,40 @@
       <c r="H31" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="J31" s="1">
         <v>34.559444399999997</v>
       </c>
-      <c r="J31" s="1">
+      <c r="K31" s="1">
         <v>135.75416670000001</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>113</v>
       </c>
       <c r="N31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="O31" s="5" t="s">
+      <c r="P31" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="R31" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R31" t="str">
+      <c r="S31" t="str">
         <f t="shared" si="1"/>
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2">
         <v>47</v>
       </c>
@@ -6920,40 +7398,43 @@
       <c r="H32" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="J32" s="1">
         <v>34.587222199999999</v>
       </c>
-      <c r="J32" s="1">
+      <c r="K32" s="1">
         <v>135.7091667</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="O32" s="5" t="s">
+      <c r="P32" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="P32" s="5" t="s">
+      <c r="Q32" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="R32" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R32" t="str">
+      <c r="S32" t="str">
         <f t="shared" si="1"/>
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2">
         <v>172</v>
       </c>
@@ -6978,36 +7459,39 @@
       <c r="H33" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="J33" s="1">
         <v>34.587222199999999</v>
       </c>
-      <c r="J33" s="1">
+      <c r="K33" s="1">
         <v>135.7091667</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="M33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M33" s="1"/>
       <c r="N33" s="1"/>
-      <c r="O33" s="4" t="s">
+      <c r="O33" s="1"/>
+      <c r="P33" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="P33" s="5" t="s">
+      <c r="Q33" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="Q33" t="str">
+      <c r="R33" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R33" t="str">
+      <c r="S33" t="str">
         <f t="shared" si="1"/>
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2">
         <v>68</v>
       </c>
@@ -7032,40 +7516,43 @@
       <c r="H34" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J34" s="1">
         <v>34.586666700000002</v>
       </c>
-      <c r="J34" s="1">
+      <c r="K34" s="1">
         <v>135.79527780000001</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="M34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O34" s="5" t="s">
+      <c r="P34" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="P34" s="6" t="s">
+      <c r="Q34" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="Q34" t="str">
+      <c r="R34" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R34" t="str">
+      <c r="S34" t="str">
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2">
         <v>61</v>
       </c>
@@ -7090,40 +7577,43 @@
       <c r="H35" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J35" s="3">
         <v>34.511944399999997</v>
       </c>
-      <c r="J35" s="1">
+      <c r="K35" s="1">
         <v>135.7586111</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="M35" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="N35" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="O35" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="O35" s="5" t="s">
+      <c r="P35" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="P35" s="6" t="s">
+      <c r="Q35" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="Q35" t="str">
+      <c r="R35" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R35" t="str">
+      <c r="S35" t="str">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2">
         <v>62</v>
       </c>
@@ -7148,37 +7638,40 @@
       <c r="H36" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I36" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J36" s="1">
         <v>34.511111100000001</v>
       </c>
-      <c r="J36" s="1">
+      <c r="K36" s="1">
         <v>135.7738889</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="M36" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="N36" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="O36" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="P36" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="Q36" t="str">
+      <c r="R36" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R36" t="str">
+      <c r="S36" t="str">
         <f t="shared" si="1"/>
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2">
         <v>64</v>
       </c>
@@ -7203,37 +7696,40 @@
       <c r="H37" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J37" s="1">
         <v>34.487777800000003</v>
       </c>
-      <c r="J37" s="1">
+      <c r="K37" s="1">
         <v>135.77722220000001</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>113</v>
       </c>
       <c r="N37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="O37" s="5" t="s">
+      <c r="P37" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="Q37" t="str">
+      <c r="R37" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R37" t="str">
+      <c r="S37" t="str">
         <f t="shared" si="1"/>
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2">
         <v>65</v>
       </c>
@@ -7258,40 +7754,43 @@
       <c r="H38" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J38" s="3">
         <v>34.506388899999997</v>
       </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
         <v>135.79277780000001</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="N38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="O38" s="5" t="s">
+      <c r="P38" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="P38" s="5" t="s">
+      <c r="Q38" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="Q38" t="str">
+      <c r="R38" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R38" t="str">
+      <c r="S38" t="str">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2">
         <v>67</v>
       </c>
@@ -7316,37 +7815,40 @@
       <c r="H39" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I39" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J39" s="1">
         <v>34.528611099999999</v>
       </c>
-      <c r="J39" s="1">
+      <c r="K39" s="1">
         <v>135.80333329999999</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>67</v>
       </c>
       <c r="N39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O39" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O39" s="5" t="s">
+      <c r="P39" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="Q39" t="str">
+      <c r="R39" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R39" t="str">
+      <c r="S39" t="str">
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2">
         <v>71</v>
       </c>
@@ -7371,37 +7873,40 @@
       <c r="H40" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I40" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J40" s="1">
         <v>34.517222199999999</v>
       </c>
-      <c r="J40" s="1">
+      <c r="K40" s="1">
         <v>135.7980556</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>73</v>
       </c>
       <c r="N40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="O40" s="5" t="s">
+      <c r="P40" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="Q40" t="str">
+      <c r="R40" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R40" t="str">
+      <c r="S40" t="str">
         <f t="shared" si="1"/>
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2">
         <v>69</v>
       </c>
@@ -7426,37 +7931,40 @@
       <c r="H41" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I41" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="J41" s="1">
         <v>34.530833299999998</v>
       </c>
-      <c r="J41" s="1">
+      <c r="K41" s="1">
         <v>135.83333329999999</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>73</v>
       </c>
       <c r="N41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="O41" s="5" t="s">
+      <c r="P41" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="Q41" t="str">
+      <c r="R41" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R41" t="str">
+      <c r="S41" t="str">
         <f t="shared" si="1"/>
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2">
         <v>70</v>
       </c>
@@ -7481,40 +7989,43 @@
       <c r="H42" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I42" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="J42" s="1">
         <v>34.517499999999998</v>
       </c>
-      <c r="J42" s="1">
+      <c r="K42" s="1">
         <v>135.86944439999999</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>15</v>
       </c>
       <c r="N42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="O42" s="5" t="s">
+      <c r="P42" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="P42" s="5" t="s">
+      <c r="Q42" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="Q42" t="str">
+      <c r="R42" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R42" t="str">
+      <c r="S42" t="str">
         <f t="shared" si="1"/>
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2">
         <v>74</v>
       </c>
@@ -7539,40 +8050,43 @@
       <c r="H43" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I43" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="J43" s="1">
         <v>34.51</v>
       </c>
-      <c r="J43" s="1">
+      <c r="K43" s="1">
         <v>135.84666669999999</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>32</v>
       </c>
       <c r="N43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O43" s="5" t="s">
+      <c r="P43" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="P43" s="6" t="s">
+      <c r="Q43" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="Q43" t="str">
+      <c r="R43" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R43" t="str">
+      <c r="S43" t="str">
         <f t="shared" si="1"/>
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2">
         <v>72</v>
       </c>
@@ -7597,40 +8111,43 @@
       <c r="H44" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I44" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J44" s="1">
         <v>34.5816667</v>
       </c>
-      <c r="J44" s="1">
+      <c r="K44" s="1">
         <v>135.7813889</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>162</v>
       </c>
       <c r="N44" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O44" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="O44" s="5" t="s">
+      <c r="P44" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="P44" s="6" t="s">
+      <c r="Q44" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="Q44" t="str">
+      <c r="R44" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R44" t="str">
+      <c r="S44" t="str">
         <f t="shared" si="1"/>
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2">
         <v>171</v>
       </c>
@@ -7655,40 +8172,43 @@
       <c r="H45" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J45" s="3">
         <v>34.5840806</v>
       </c>
-      <c r="J45" s="1">
+      <c r="K45" s="1">
         <v>135.7510833</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="M45" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="N45" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="O45" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="O45" s="5" t="s">
+      <c r="P45" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="P45" s="6" t="s">
+      <c r="Q45" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="Q45" t="str">
+      <c r="R45" t="str">
         <f t="shared" si="0"/>
         <v>22069</v>
       </c>
-      <c r="R45" t="str">
+      <c r="S45" t="str">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2">
         <v>75</v>
       </c>
@@ -7713,40 +8233,43 @@
       <c r="H46" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="I46" s="1">
+      <c r="I46" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="J46" s="1">
         <v>34.566944399999997</v>
       </c>
-      <c r="J46" s="1">
+      <c r="K46" s="1">
         <v>135.76972219999999</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="N46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O46" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="O46" s="5" t="s">
+      <c r="P46" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="P46" s="5" t="s">
+      <c r="Q46" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="Q46" t="str">
+      <c r="R46" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R46" t="str">
+      <c r="S46" t="str">
         <f t="shared" si="1"/>
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2">
         <v>76</v>
       </c>
@@ -7771,40 +8294,43 @@
       <c r="H47" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I47" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="J47" s="1">
         <v>34.571388900000002</v>
       </c>
-      <c r="J47" s="1">
+      <c r="K47" s="1">
         <v>135.7630556</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="N47" s="1" t="s">
+      <c r="O47" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="O47" s="5" t="s">
+      <c r="P47" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="P47" s="6" t="s">
+      <c r="Q47" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="Q47" t="str">
+      <c r="R47" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R47" t="str">
+      <c r="S47" t="str">
         <f t="shared" si="1"/>
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2">
         <v>66</v>
       </c>
@@ -7829,40 +8355,43 @@
       <c r="H48" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I48" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J48" s="1">
         <v>34.545000000000002</v>
       </c>
-      <c r="J48" s="1">
+      <c r="K48" s="1">
         <v>135.7955556</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>145</v>
       </c>
       <c r="N48" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="O48" s="5" t="s">
+      <c r="P48" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="P48" s="5" t="s">
+      <c r="Q48" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="Q48" t="str">
+      <c r="R48" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R48" t="str">
+      <c r="S48" t="str">
         <f t="shared" si="1"/>
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2">
         <v>63</v>
       </c>
@@ -7887,37 +8416,40 @@
       <c r="H49" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I49" s="1">
+      <c r="I49" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="J49" s="1">
         <v>34.457500000000003</v>
       </c>
-      <c r="J49" s="1">
+      <c r="K49" s="1">
         <v>135.76388890000001</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="M49" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="N49" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N49" s="1" t="s">
+      <c r="O49" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O49" s="5" t="s">
+      <c r="P49" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="Q49" t="str">
+      <c r="R49" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R49" t="str">
+      <c r="S49" t="str">
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2">
         <v>73</v>
       </c>
@@ -7942,40 +8474,43 @@
       <c r="H50" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J50" s="1">
         <v>34.463888900000001</v>
       </c>
-      <c r="J50" s="1">
+      <c r="K50" s="1">
         <v>135.79861109999999</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="N50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O50" s="5" t="s">
+      <c r="P50" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="P50" s="5" t="s">
+      <c r="Q50" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="Q50" t="str">
+      <c r="R50" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R50" t="str">
+      <c r="S50" t="str">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2">
         <v>77</v>
       </c>
@@ -8000,40 +8535,43 @@
       <c r="H51" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I51" s="1">
+      <c r="I51" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J51" s="1">
         <v>34.4808333</v>
       </c>
-      <c r="J51" s="1">
+      <c r="K51" s="1">
         <v>135.8172222</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>37</v>
       </c>
       <c r="N51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O51" s="5" t="s">
+      <c r="P51" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="P51" s="6" t="s">
+      <c r="Q51" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="Q51" t="str">
+      <c r="R51" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R51" t="str">
+      <c r="S51" t="str">
         <f t="shared" si="1"/>
         <v>154</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="2">
         <v>91</v>
       </c>
@@ -8058,40 +8596,43 @@
       <c r="H52" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I52" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J52" s="1">
         <v>34.527777800000003</v>
       </c>
-      <c r="J52" s="1">
+      <c r="K52" s="1">
         <v>135.9566667</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="N52" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N52" s="1" t="s">
+      <c r="O52" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="O52" s="5" t="s">
+      <c r="P52" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="P52" s="6" t="s">
+      <c r="Q52" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="Q52" t="str">
+      <c r="R52" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R52" t="str">
+      <c r="S52" t="str">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="2">
         <v>92</v>
       </c>
@@ -8116,40 +8657,43 @@
       <c r="H53" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I53" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J53" s="1">
         <v>34.482777800000001</v>
       </c>
-      <c r="J53" s="1">
+      <c r="K53" s="1">
         <v>135.93055559999999</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>66</v>
       </c>
       <c r="N53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O53" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O53" s="5" t="s">
+      <c r="P53" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="P53" s="6" t="s">
+      <c r="Q53" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="Q53" t="str">
+      <c r="R53" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R53" t="str">
+      <c r="S53" t="str">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="2">
         <v>94</v>
       </c>
@@ -8174,40 +8718,43 @@
       <c r="H54" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I54" s="1">
+      <c r="I54" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J54" s="1">
         <v>34.478888900000001</v>
       </c>
-      <c r="J54" s="1">
+      <c r="K54" s="1">
         <v>135.96416669999999</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="L54" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="N54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O54" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O54" s="5" t="s">
+      <c r="P54" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="P54" s="6" t="s">
+      <c r="Q54" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="Q54" t="str">
+      <c r="R54" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R54" t="str">
+      <c r="S54" t="str">
         <f t="shared" si="1"/>
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="2">
         <v>151</v>
       </c>
@@ -8232,29 +8779,32 @@
       <c r="H55" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="I55" s="1">
+      <c r="I55" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J55" s="1">
         <v>34.5283333</v>
       </c>
-      <c r="J55" s="1">
+      <c r="K55" s="1">
         <v>135.97499999999999</v>
       </c>
-      <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
-      <c r="O55" s="4" t="s">
+      <c r="O55" s="1"/>
+      <c r="P55" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="Q55" t="str">
+      <c r="R55" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R55" t="str">
+      <c r="S55" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="2">
         <v>152</v>
       </c>
@@ -8279,32 +8829,35 @@
       <c r="H56" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I56" s="1">
+      <c r="I56" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J56" s="1">
         <v>34.561388899999997</v>
       </c>
-      <c r="J56" s="1">
+      <c r="K56" s="1">
         <v>136.01527780000001</v>
       </c>
-      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
-      <c r="O56" s="4" t="s">
+      <c r="O56" s="1"/>
+      <c r="P56" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="P56" s="4" t="s">
+      <c r="Q56" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="Q56" t="str">
+      <c r="R56" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R56" t="str">
+      <c r="S56" t="str">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="2">
         <v>155</v>
       </c>
@@ -8329,29 +8882,32 @@
       <c r="H57" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="I57" s="1">
+      <c r="I57" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J57" s="1">
         <v>34.526944399999998</v>
       </c>
-      <c r="J57" s="1">
+      <c r="K57" s="1">
         <v>135.95249999999999</v>
       </c>
-      <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
-      <c r="O57" s="4" t="s">
+      <c r="O57" s="1"/>
+      <c r="P57" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="Q57" t="str">
+      <c r="R57" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R57" t="str">
+      <c r="S57" t="str">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="2">
         <v>95</v>
       </c>
@@ -8376,32 +8932,35 @@
       <c r="H58" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="I58" s="1">
+      <c r="I58" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J58" s="1">
         <v>34.510277799999997</v>
       </c>
-      <c r="J58" s="1">
+      <c r="K58" s="1">
         <v>136.12555560000001</v>
       </c>
-      <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
-      <c r="O58" s="4" t="s">
+      <c r="O58" s="1"/>
+      <c r="P58" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="P58" s="4" t="s">
+      <c r="Q58" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="Q58" t="str">
+      <c r="R58" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R58" t="str">
+      <c r="S58" t="str">
         <f t="shared" si="1"/>
         <v>155</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="2">
         <v>153</v>
       </c>
@@ -8426,36 +8985,39 @@
       <c r="H59" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I59" s="1">
+      <c r="I59" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="J59" s="1">
         <v>34.553159999999998</v>
       </c>
-      <c r="J59" s="1">
+      <c r="K59" s="1">
         <v>136.13637199999999</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="L59" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M59" s="1"/>
       <c r="N59" s="1"/>
-      <c r="O59" s="4" t="s">
+      <c r="O59" s="1"/>
+      <c r="P59" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="P59" s="4" t="s">
+      <c r="Q59" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="Q59" t="str">
+      <c r="R59" t="str">
         <f t="shared" si="0"/>
         <v>22067</v>
       </c>
-      <c r="R59" t="str">
+      <c r="S59" t="str">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="2">
         <v>93</v>
       </c>
@@ -8480,40 +9042,43 @@
       <c r="H60" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I60" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J60" s="1">
         <v>34.403611099999999</v>
       </c>
-      <c r="J60" s="1">
+      <c r="K60" s="1">
         <v>135.96805560000001</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="L60" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>173</v>
       </c>
       <c r="N60" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O60" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="O60" s="5" t="s">
+      <c r="P60" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="P60" s="6" t="s">
+      <c r="Q60" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="Q60" t="str">
+      <c r="R60" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R60" t="str">
+      <c r="S60" t="str">
         <f t="shared" si="1"/>
         <v>122</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="2">
         <v>193</v>
       </c>
@@ -8538,29 +9103,32 @@
       <c r="H61" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I61" s="1">
+      <c r="I61" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J61" s="1">
         <v>34.399722199999999</v>
       </c>
-      <c r="J61" s="1">
+      <c r="K61" s="1">
         <v>135.9652778</v>
       </c>
-      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
-      <c r="O61" s="4" t="s">
+      <c r="O61" s="1"/>
+      <c r="P61" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="Q61" t="str">
+      <c r="R61" t="str">
         <f t="shared" si="0"/>
         <v>22077</v>
       </c>
-      <c r="R61" t="str">
+      <c r="S61" t="str">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="2">
         <v>111</v>
       </c>
@@ -8585,40 +9153,43 @@
       <c r="H62" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="I62" s="1">
+      <c r="I62" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="J62" s="1">
         <v>34.393333300000002</v>
       </c>
-      <c r="J62" s="1">
+      <c r="K62" s="1">
         <v>135.8511111</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>213</v>
       </c>
       <c r="N62" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O62" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="O62" s="5" t="s">
+      <c r="P62" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="P62" s="5" t="s">
+      <c r="Q62" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="Q62" t="str">
+      <c r="R62" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R62" t="str">
+      <c r="S62" t="str">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="2">
         <v>114</v>
       </c>
@@ -8643,37 +9214,40 @@
       <c r="H63" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I63" s="1">
+      <c r="I63" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="J63" s="1">
         <v>34.385555600000004</v>
       </c>
-      <c r="J63" s="1">
+      <c r="K63" s="1">
         <v>135.90111110000001</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="L63" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="M63" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="N63" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="N63" s="1" t="s">
+      <c r="O63" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="O63" s="5" t="s">
+      <c r="P63" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="Q63" t="str">
+      <c r="R63" t="str">
         <f t="shared" si="0"/>
         <v>7425</v>
       </c>
-      <c r="R63" t="str">
+      <c r="S63" t="str">
         <f t="shared" si="1"/>
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="2">
         <v>187</v>
       </c>
@@ -8698,30 +9272,33 @@
       <c r="H64" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="I64" s="1">
+      <c r="I64" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="J64" s="1">
         <v>34.393055599999997</v>
       </c>
-      <c r="J64" s="1">
+      <c r="K64" s="1">
         <v>135.86972220000001</v>
       </c>
-      <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
-      <c r="O64" s="4" t="s">
+      <c r="O64" s="1"/>
+      <c r="P64" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="P64" s="4"/>
-      <c r="Q64" t="str">
+      <c r="Q64" s="4"/>
+      <c r="R64" t="str">
         <f t="shared" si="0"/>
         <v>22077</v>
       </c>
-      <c r="R64" t="str">
+      <c r="S64" t="str">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="2">
         <v>115</v>
       </c>
@@ -8746,40 +9323,43 @@
       <c r="H65" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I65" s="1">
+      <c r="I65" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="J65" s="1">
         <v>34.383333299999997</v>
       </c>
-      <c r="J65" s="1">
+      <c r="K65" s="1">
         <v>135.77916669999999</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="L65" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="M65" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="N65" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N65" s="1" t="s">
+      <c r="O65" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="O65" s="4" t="s">
+      <c r="P65" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="P65" s="5" t="s">
+      <c r="Q65" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="Q65" t="str">
-        <f t="shared" ref="Q65:Q76" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(O65,"ofcCd="),"&amp;")</f>
+      <c r="R65" t="str">
+        <f t="shared" ref="R65:R76" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(P65,"ofcCd="),"&amp;")</f>
         <v>7425</v>
       </c>
-      <c r="R65" t="str">
-        <f t="shared" ref="R65:R76" si="3">_xlfn.TEXTAFTER(O65,"obsCd=")</f>
+      <c r="S65" t="str">
+        <f t="shared" ref="S65:S76" si="3">_xlfn.TEXTAFTER(P65,"obsCd=")</f>
         <v>157</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="2">
         <v>116</v>
       </c>
@@ -8804,29 +9384,32 @@
       <c r="H66" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I66" s="1">
+      <c r="I66" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J66" s="1">
         <v>34.369166700000001</v>
       </c>
-      <c r="J66" s="1">
+      <c r="K66" s="1">
         <v>135.78944440000001</v>
       </c>
-      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
-      <c r="O66" s="4" t="s">
+      <c r="O66" s="1"/>
+      <c r="P66" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="Q66" t="str">
+      <c r="R66" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R66" t="str">
+      <c r="S66" t="str">
         <f t="shared" si="3"/>
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="2">
         <v>113</v>
       </c>
@@ -8851,29 +9434,32 @@
       <c r="H67" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="I67" s="1">
+      <c r="I67" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="J67" s="1">
         <v>34.1952778</v>
       </c>
-      <c r="J67" s="1">
+      <c r="K67" s="1">
         <v>135.80444439999999</v>
       </c>
-      <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
-      <c r="O67" s="4" t="s">
+      <c r="O67" s="1"/>
+      <c r="P67" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="Q67" t="str">
+      <c r="R67" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R67" t="str">
+      <c r="S67" t="str">
         <f t="shared" si="3"/>
         <v>139</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="2">
         <v>112</v>
       </c>
@@ -8898,37 +9484,40 @@
       <c r="H68" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="I68" s="1">
+      <c r="I68" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="J68" s="1">
         <v>34.366111099999998</v>
       </c>
-      <c r="J68" s="1">
+      <c r="K68" s="1">
         <v>135.93916669999999</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="N68" s="1" t="s">
+      <c r="O68" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="O68" s="5" t="s">
+      <c r="P68" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="Q68" t="str">
+      <c r="R68" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R68" t="str">
+      <c r="S68" t="str">
         <f t="shared" si="3"/>
         <v>124</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="2">
         <v>131</v>
       </c>
@@ -8953,37 +9542,40 @@
       <c r="H69" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="I69" s="1">
+      <c r="I69" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="J69" s="1">
         <v>34.355555600000002</v>
       </c>
-      <c r="J69" s="1">
+      <c r="K69" s="1">
         <v>135.71916669999999</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="L69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="M69" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="N69" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="O69" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="O69" s="5" t="s">
+      <c r="P69" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="Q69" t="str">
+      <c r="R69" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R69" t="str">
+      <c r="S69" t="str">
         <f t="shared" si="3"/>
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="2">
         <v>136</v>
       </c>
@@ -9008,40 +9600,43 @@
       <c r="H70" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="I70" s="1">
+      <c r="I70" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="J70" s="1">
         <v>34.2822222</v>
       </c>
-      <c r="J70" s="1">
+      <c r="K70" s="1">
         <v>135.7475</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="M70" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="N70" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="O70" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="O70" s="5" t="s">
+      <c r="P70" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="P70" s="5" t="s">
+      <c r="Q70" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="Q70" t="str">
+      <c r="R70" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R70" t="str">
+      <c r="S70" t="str">
         <f t="shared" si="3"/>
         <v>159</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="2">
         <v>190</v>
       </c>
@@ -9066,30 +9661,33 @@
       <c r="H71" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="I71" s="1">
+      <c r="I71" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J71" s="1">
         <v>34.167222199999998</v>
       </c>
-      <c r="J71" s="1">
+      <c r="K71" s="1">
         <v>135.75666670000001</v>
       </c>
-      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
-      <c r="O71" s="4" t="s">
+      <c r="O71" s="1"/>
+      <c r="P71" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="P71" s="4"/>
-      <c r="Q71" t="str">
+      <c r="Q71" s="4"/>
+      <c r="R71" t="str">
         <f t="shared" si="2"/>
         <v>22077</v>
       </c>
-      <c r="R71" t="str">
+      <c r="S71" t="str">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="2">
         <v>204</v>
       </c>
@@ -9114,40 +9712,43 @@
       <c r="H72" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="I72" s="1">
+      <c r="I72" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="J72" s="1">
         <v>34.346944399999998</v>
       </c>
-      <c r="J72" s="1">
+      <c r="K72" s="1">
         <v>135.69194440000001</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="L72" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="L72" s="1" t="s">
+      <c r="M72" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="M72" s="1" t="s">
+      <c r="N72" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="N72" s="1" t="s">
+      <c r="O72" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="O72" s="5" t="s">
+      <c r="P72" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="P72" s="6" t="s">
+      <c r="Q72" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="Q72" t="str">
+      <c r="R72" t="str">
         <f t="shared" si="2"/>
         <v>22087</v>
       </c>
-      <c r="R72" t="str">
+      <c r="S72" t="str">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="2">
         <v>132</v>
       </c>
@@ -9172,37 +9773,40 @@
       <c r="H73" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I73" s="1">
+      <c r="I73" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J73" s="1">
         <v>34.294722200000002</v>
       </c>
-      <c r="J73" s="1">
+      <c r="K73" s="1">
         <v>135.78555560000001</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="L73" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>74</v>
       </c>
       <c r="N73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O73" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="O73" s="5" t="s">
+      <c r="P73" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="Q73" t="str">
+      <c r="R73" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R73" t="str">
+      <c r="S73" t="str">
         <f t="shared" si="3"/>
         <v>126</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="2">
         <v>133</v>
       </c>
@@ -9227,29 +9831,32 @@
       <c r="H74" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="I74" s="1">
+      <c r="I74" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="J74" s="1">
         <v>34.012777800000002</v>
       </c>
-      <c r="J74" s="1">
+      <c r="K74" s="1">
         <v>135.7955556</v>
       </c>
-      <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
-      <c r="O74" s="4" t="s">
+      <c r="O74" s="1"/>
+      <c r="P74" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="Q74" t="str">
+      <c r="R74" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R74" t="str">
+      <c r="S74" t="str">
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="2">
         <v>134</v>
       </c>
@@ -9274,29 +9881,32 @@
       <c r="H75" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="I75" s="1">
+      <c r="I75" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="J75" s="1">
         <v>34.038333299999998</v>
       </c>
-      <c r="J75" s="1">
+      <c r="K75" s="1">
         <v>135.7897222</v>
       </c>
-      <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
-      <c r="O75" s="4" t="s">
+      <c r="O75" s="1"/>
+      <c r="P75" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="Q75" t="str">
+      <c r="R75" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R75" t="str">
+      <c r="S75" t="str">
         <f t="shared" si="3"/>
         <v>141</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="2">
         <v>135</v>
       </c>
@@ -9321,24 +9931,27 @@
       <c r="H76" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="I76" s="1">
+      <c r="I76" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="J76" s="1">
         <v>34.1097222</v>
       </c>
-      <c r="J76" s="1">
+      <c r="K76" s="1">
         <v>135.77444439999999</v>
       </c>
-      <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
-      <c r="O76" s="4" t="s">
+      <c r="O76" s="1"/>
+      <c r="P76" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="Q76" t="str">
+      <c r="R76" t="str">
         <f t="shared" si="2"/>
         <v>7425</v>
       </c>
-      <c r="R76" t="str">
+      <c r="S76" t="str">
         <f t="shared" si="3"/>
         <v>142</v>
       </c>
@@ -9346,125 +9959,125 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="O15" r:id="rId1" xr:uid="{80AF0F52-FE9E-4459-A83E-04FBE851D5F9}"/>
-    <hyperlink ref="O2" r:id="rId2" xr:uid="{5E959C54-3B96-4308-B0CF-766C1C618472}"/>
-    <hyperlink ref="P2" r:id="rId3" xr:uid="{DD420838-FEC6-42C5-AC03-45C106F8EC09}"/>
-    <hyperlink ref="O3" r:id="rId4" xr:uid="{E3440A7A-9DF5-4BD2-ABB1-AFF25B04F4AC}"/>
-    <hyperlink ref="P3" r:id="rId5" xr:uid="{2C197A79-4E8D-4A85-A96C-97A0E1307524}"/>
-    <hyperlink ref="O4" r:id="rId6" xr:uid="{A67ED444-F017-41F1-8FCD-030E9CB2CED6}"/>
-    <hyperlink ref="P4" r:id="rId7" xr:uid="{91F5747B-B161-47E0-A8CD-57C4EC6A89BA}"/>
-    <hyperlink ref="O5" r:id="rId8" xr:uid="{FB845758-F2B7-4FCB-B9C4-9D277957A9C2}"/>
-    <hyperlink ref="O6" r:id="rId9" xr:uid="{86DAB206-CE0A-452F-9861-95F49A78368A}"/>
-    <hyperlink ref="P6" r:id="rId10" xr:uid="{6F5FA695-FD59-410E-9551-BDB0967C9BDB}"/>
-    <hyperlink ref="O7" r:id="rId11" xr:uid="{9E558C1F-9F50-4399-8E48-895D64753BB8}"/>
-    <hyperlink ref="O8" r:id="rId12" xr:uid="{CD4C5C91-1C21-4A19-A20C-3BA4AFA96220}"/>
-    <hyperlink ref="O9" r:id="rId13" xr:uid="{3106ED78-709C-4593-9CA3-060B12000B9F}"/>
-    <hyperlink ref="P9" r:id="rId14" xr:uid="{B8BB7C6A-F612-4DD7-9842-68272B9974AD}"/>
-    <hyperlink ref="O10" r:id="rId15" xr:uid="{B859F619-414F-4EF9-8626-9F45BA0CEBB8}"/>
-    <hyperlink ref="P10" r:id="rId16" xr:uid="{55685B34-15DA-4989-94D6-8C134922781E}"/>
-    <hyperlink ref="O11" r:id="rId17" xr:uid="{865402AF-1612-4FD1-89F5-9103C95E5141}"/>
-    <hyperlink ref="P11" r:id="rId18" xr:uid="{7174D598-EC3F-483C-BDB8-869E0B8AF361}"/>
-    <hyperlink ref="O12" r:id="rId19" xr:uid="{8EB138DE-3548-4935-B8BA-A80F332C7547}"/>
-    <hyperlink ref="O13" r:id="rId20" xr:uid="{030979C6-729A-4CA8-9863-F034B29531B8}"/>
-    <hyperlink ref="O14" r:id="rId21" xr:uid="{E78B413F-4E33-4E43-BDE8-193FD47A4F40}"/>
-    <hyperlink ref="O16" r:id="rId22" xr:uid="{6E14F61A-3A44-46F4-A1EA-8D425ED4615E}"/>
-    <hyperlink ref="P16" r:id="rId23" xr:uid="{6F3EDC96-F2AB-4C90-AAF5-A2A12B08768E}"/>
-    <hyperlink ref="O17" r:id="rId24" xr:uid="{AE4725A0-887A-46C6-99E7-958FE5BDCB0C}"/>
-    <hyperlink ref="P17" r:id="rId25" xr:uid="{4D2F612B-1939-4980-8A2E-3270FE5C5409}"/>
-    <hyperlink ref="O18" r:id="rId26" xr:uid="{AE2C6CBC-91AE-44C0-BEAF-5B0B25CEEC7C}"/>
-    <hyperlink ref="P18" r:id="rId27" xr:uid="{4AE79112-0011-41D4-ACF5-D4C1F8131FED}"/>
-    <hyperlink ref="O19" r:id="rId28" xr:uid="{154A5634-4EBA-4291-9D79-20044072C061}"/>
-    <hyperlink ref="O20" r:id="rId29" xr:uid="{B7265333-C422-41BB-8F01-A13EB946490A}"/>
-    <hyperlink ref="P20" r:id="rId30" xr:uid="{E9056260-8DF8-48B1-AE3F-6FC0DFCAC1BA}"/>
-    <hyperlink ref="O21" r:id="rId31" xr:uid="{B5DAA74E-2CC7-4511-B54D-5C7787744C06}"/>
-    <hyperlink ref="O22" r:id="rId32" xr:uid="{9826A3E7-34D5-4B6D-8312-BB8F1CF8D9B1}"/>
-    <hyperlink ref="P22" r:id="rId33" display="https://www.river.go.jp/kawabou/pc/tm?zm=12&amp;clat=34.60241096129153&amp;clon=135.76938629150393&amp;fld=0&amp;mapType=0&amp;viewGrpStg=0&amp;viewRd=1&amp;viewRW=1&amp;viewRl=1&amp;viewRn=1&amp;viewPoint=1&amp;ext=0&amp;itmkndCd=200&amp;scamId=107425042&amp;ownCd=7425&amp;sysCamId=7425042" xr:uid="{DA1DF261-6A32-429E-A114-E2B2F6548233}"/>
-    <hyperlink ref="O23" r:id="rId34" xr:uid="{232C94BD-E4E6-4EF8-AE62-28BD905E1A6C}"/>
-    <hyperlink ref="O24" r:id="rId35" xr:uid="{E3796CE5-9C4D-4BE3-A426-114230918EC8}"/>
-    <hyperlink ref="P24" r:id="rId36" xr:uid="{1E40C976-7E5A-4740-BE13-5B483E23AD72}"/>
-    <hyperlink ref="O25" r:id="rId37" xr:uid="{BCA65EBC-E59E-49CA-864A-7EDC309DCBA0}"/>
-    <hyperlink ref="O26" r:id="rId38" xr:uid="{03B784DC-ABEB-4E38-B1D4-09A032EFB5F1}"/>
-    <hyperlink ref="O27" r:id="rId39" xr:uid="{761BC090-EC91-480E-A1DD-1AD3ADC583CF}"/>
-    <hyperlink ref="O28" r:id="rId40" xr:uid="{1D1FD9CF-3BF7-4F53-886F-EF8F770963C3}"/>
-    <hyperlink ref="P28" r:id="rId41" xr:uid="{BC9B9A13-6428-4833-95E2-7DAD4AF55AD4}"/>
-    <hyperlink ref="O29" r:id="rId42" xr:uid="{BCD1C373-B69E-4366-B759-FE73F6C96251}"/>
-    <hyperlink ref="P29" r:id="rId43" xr:uid="{C81E2CD2-DFA0-4F64-8373-112209FBDE4E}"/>
-    <hyperlink ref="O30" r:id="rId44" xr:uid="{33441477-EA47-4147-8361-D36451B51ADF}"/>
-    <hyperlink ref="O31" r:id="rId45" xr:uid="{60077CF3-A9E2-4AF4-9DC4-B8066C8AE43E}"/>
-    <hyperlink ref="O32" r:id="rId46" xr:uid="{4B33F0E6-8FC6-4531-877B-110204908392}"/>
-    <hyperlink ref="O33" r:id="rId47" xr:uid="{3AF0EBDD-6107-471E-BF9D-A8F62FD0E727}"/>
-    <hyperlink ref="P33" r:id="rId48" xr:uid="{70F24105-5F61-4BA5-9D08-6A7F0A0C8BB4}"/>
-    <hyperlink ref="O34" r:id="rId49" xr:uid="{64CCD285-2A46-4D83-BB11-8B0ADE7C30BB}"/>
-    <hyperlink ref="P34" r:id="rId50" xr:uid="{A6C9C94A-AE6B-4354-8159-84525A85A490}"/>
-    <hyperlink ref="O35" r:id="rId51" xr:uid="{7BFF2452-A754-4B8B-A2D9-8A9DF535A2E7}"/>
-    <hyperlink ref="P35" r:id="rId52" xr:uid="{E831222A-9F5C-482A-9142-E0FB5BDBBF7D}"/>
-    <hyperlink ref="O36" r:id="rId53" xr:uid="{0EA32899-BE39-459F-A75F-19F2A2CACFBC}"/>
-    <hyperlink ref="O37" r:id="rId54" xr:uid="{7AA35659-E8FF-4AFC-B878-ADF477A380B7}"/>
-    <hyperlink ref="O38" r:id="rId55" xr:uid="{76AF3A8B-0A6B-4F0F-9147-F819C4161658}"/>
-    <hyperlink ref="O39" r:id="rId56" xr:uid="{DDAE6DE0-0B74-48B2-8BB5-5D092752F32D}"/>
-    <hyperlink ref="O40" r:id="rId57" xr:uid="{D7314B06-3C86-4473-8603-F94080C2AF3F}"/>
-    <hyperlink ref="O41" r:id="rId58" xr:uid="{91A5565A-5A71-4A32-99AF-2704D12340EE}"/>
-    <hyperlink ref="O42" r:id="rId59" xr:uid="{567BA0F0-BD1D-46CD-8516-2F0ACCD8D2B5}"/>
-    <hyperlink ref="P42" r:id="rId60" xr:uid="{DD6A56A7-61D7-4C94-9E2D-D093294E8576}"/>
-    <hyperlink ref="O43" r:id="rId61" xr:uid="{F5EE3DE8-0194-4FF2-8B4B-E06078566D82}"/>
-    <hyperlink ref="O44" r:id="rId62" xr:uid="{7A139CC9-CC03-43B4-A26B-22132F2D00DD}"/>
-    <hyperlink ref="P44" r:id="rId63" xr:uid="{219C3CF3-8803-4E1D-9F8C-54AD57B46C2E}"/>
-    <hyperlink ref="O45" r:id="rId64" xr:uid="{A93AD36D-52BE-48CF-8D41-48B09B834FB2}"/>
-    <hyperlink ref="P45" r:id="rId65" xr:uid="{4F074575-4A63-4DA9-B682-95245C34D028}"/>
-    <hyperlink ref="P46" r:id="rId66" xr:uid="{DEF28B44-B0DE-40EB-BC49-D84DF0889A84}"/>
-    <hyperlink ref="O46" r:id="rId67" xr:uid="{F46B48A4-C76F-4830-B8EC-AD38D7D38BD3}"/>
-    <hyperlink ref="O47" r:id="rId68" xr:uid="{A5078E1A-0274-4D2F-8205-356E668543A8}"/>
-    <hyperlink ref="O48" r:id="rId69" xr:uid="{299921A5-1E2D-4CC2-B084-3E4A1470A88D}"/>
-    <hyperlink ref="P48" r:id="rId70" xr:uid="{1494FC1D-5B07-4ED2-9E2E-B26EAC276805}"/>
-    <hyperlink ref="O49" r:id="rId71" xr:uid="{D03F1817-E00E-4F69-AD8F-9C0EBBA8E8BC}"/>
-    <hyperlink ref="O50" r:id="rId72" xr:uid="{3069C10A-9C10-4333-886D-7E2DDE826DEE}"/>
-    <hyperlink ref="P50" r:id="rId73" xr:uid="{AE733813-0DB9-4200-B20A-3376496AEB7F}"/>
-    <hyperlink ref="O51" r:id="rId74" xr:uid="{F2443606-D331-4786-BAC7-6896BFCECFF0}"/>
-    <hyperlink ref="P51" r:id="rId75" xr:uid="{DC99C0E7-F0E5-4042-B048-3E31BD1DF48D}"/>
-    <hyperlink ref="O52" r:id="rId76" xr:uid="{624C851A-6C89-4CC0-A219-B18F3A06C35A}"/>
-    <hyperlink ref="P52" r:id="rId77" xr:uid="{EFE49E4B-7BEC-4B89-A015-D646BA9B9951}"/>
-    <hyperlink ref="O53" r:id="rId78" xr:uid="{91E4958D-9FED-453C-9238-7A0EBF24DDA0}"/>
-    <hyperlink ref="P53" r:id="rId79" xr:uid="{5DDD53DC-F31C-4321-BE2C-81076DE0B813}"/>
-    <hyperlink ref="O54" r:id="rId80" xr:uid="{BD6CEAB1-F5BF-48EB-B476-B1CA03B6792C}"/>
-    <hyperlink ref="P54" r:id="rId81" xr:uid="{637C6B19-6DA4-42D4-A59A-962FAB655863}"/>
-    <hyperlink ref="O55" r:id="rId82" xr:uid="{37F4E260-CCBC-4790-A8E6-366E907778D3}"/>
-    <hyperlink ref="O56" r:id="rId83" xr:uid="{50728D18-80A2-41C9-9684-71EA672643A9}"/>
-    <hyperlink ref="O57" r:id="rId84" xr:uid="{84506F98-72FF-479B-8A89-5F966E562F30}"/>
-    <hyperlink ref="P58" r:id="rId85" xr:uid="{A86E6E98-036A-4DF0-9ED2-826A0909C637}"/>
-    <hyperlink ref="P56" r:id="rId86" xr:uid="{591132DA-6FDD-46B8-9B34-50E4B30C2326}"/>
-    <hyperlink ref="O58" r:id="rId87" xr:uid="{0362DE56-C757-49DA-A2CA-955756DD3CCA}"/>
-    <hyperlink ref="P59" r:id="rId88" xr:uid="{6BF187E7-C20D-4B10-AA4F-FA6075A39F95}"/>
-    <hyperlink ref="O59" r:id="rId89" xr:uid="{11EE20EB-F8A8-4D0A-81AB-7B63150DF82B}"/>
-    <hyperlink ref="O60" r:id="rId90" xr:uid="{01A3C01F-4051-4E83-9E5A-1E98B5CA9CC7}"/>
-    <hyperlink ref="P60" r:id="rId91" xr:uid="{24C3792C-A3AE-4FC5-9109-1C2FD4D09EB0}"/>
-    <hyperlink ref="O62" r:id="rId92" xr:uid="{6B9D1916-F27D-4F02-8A42-18975E2E36EA}"/>
-    <hyperlink ref="P62" r:id="rId93" xr:uid="{071CEDC8-7D72-4C11-9945-DED6C41A8B1E}"/>
-    <hyperlink ref="O63" r:id="rId94" xr:uid="{0B03128E-2C50-4B1D-B2DE-77E1B45714F3}"/>
-    <hyperlink ref="O61" r:id="rId95" xr:uid="{E5EE7183-E9F5-457B-A884-E40763AC314A}"/>
-    <hyperlink ref="O64" r:id="rId96" xr:uid="{8C44961E-4772-465F-A837-8EA48FA3CEA6}"/>
-    <hyperlink ref="O65" r:id="rId97" xr:uid="{E937E12F-2628-45E0-8260-0E703214499D}"/>
-    <hyperlink ref="P65" r:id="rId98" xr:uid="{5E41DCA2-3AED-46D9-BC02-3E082D847A97}"/>
-    <hyperlink ref="O66" r:id="rId99" xr:uid="{67003E07-4EED-4ADA-8325-2F767337709A}"/>
-    <hyperlink ref="O71" r:id="rId100" xr:uid="{8826EBFB-91BB-443B-896A-E284D64A6E0A}"/>
-    <hyperlink ref="O67" r:id="rId101" xr:uid="{C54722E9-BD3E-4C18-953D-D1515B485902}"/>
-    <hyperlink ref="O68" r:id="rId102" xr:uid="{B907FE13-5849-4C10-AE8D-B2FE098659CE}"/>
-    <hyperlink ref="O69" r:id="rId103" xr:uid="{9B4FE783-ECE6-4692-AAD8-93605DF44DF4}"/>
-    <hyperlink ref="O70" r:id="rId104" xr:uid="{948B94EE-FB54-44C6-B50E-2DA23BB32796}"/>
-    <hyperlink ref="O72" r:id="rId105" xr:uid="{A411935B-1994-4049-8FF0-28FB42096408}"/>
-    <hyperlink ref="P72" r:id="rId106" xr:uid="{2A76E0A4-EC10-4967-84E2-00BED5D358B3}"/>
-    <hyperlink ref="O73" r:id="rId107" xr:uid="{8EA3C855-2234-4C55-B597-13F9400E0BD0}"/>
-    <hyperlink ref="O74" r:id="rId108" xr:uid="{C4D2A0FA-2525-4F04-AEA8-7AB6E72B8789}"/>
-    <hyperlink ref="O75" r:id="rId109" xr:uid="{0D5A9C33-8FE8-403D-84EB-16AA4CB4AE04}"/>
-    <hyperlink ref="O76" r:id="rId110" xr:uid="{E01CEFD8-9FEC-4146-8A24-40D28CEFF048}"/>
-    <hyperlink ref="P15" r:id="rId111" xr:uid="{5B72FD30-5AC0-4947-B9E9-5D1E55ECFC1C}"/>
-    <hyperlink ref="P25" r:id="rId112" xr:uid="{1F40BFD5-1664-4B8E-9AD0-04899D1DF1D1}"/>
-    <hyperlink ref="P23" r:id="rId113" xr:uid="{EA4009B5-D4FF-46BE-962D-5307A513DFE2}"/>
-    <hyperlink ref="P30" r:id="rId114" xr:uid="{4C90473C-163E-4562-BED7-C580B121271C}"/>
-    <hyperlink ref="P32" r:id="rId115" xr:uid="{476D1F67-6A1A-41C9-A843-3B3FC63DE9A7}"/>
-    <hyperlink ref="P38" r:id="rId116" xr:uid="{8F7D7FA1-3D5E-4BF5-92E2-A491876D2137}"/>
-    <hyperlink ref="P43" r:id="rId117" xr:uid="{F9E60127-FA03-468B-A56D-60844C91CFF6}"/>
-    <hyperlink ref="P47" r:id="rId118" xr:uid="{F0FB7F74-3E66-47AE-B1A1-1401657ACFCA}"/>
-    <hyperlink ref="P70" r:id="rId119" xr:uid="{E5C917D2-559D-41F8-A179-79AEF2730A64}"/>
+    <hyperlink ref="P15" r:id="rId1" xr:uid="{80AF0F52-FE9E-4459-A83E-04FBE851D5F9}"/>
+    <hyperlink ref="P2" r:id="rId2" xr:uid="{5E959C54-3B96-4308-B0CF-766C1C618472}"/>
+    <hyperlink ref="Q2" r:id="rId3" xr:uid="{DD420838-FEC6-42C5-AC03-45C106F8EC09}"/>
+    <hyperlink ref="P3" r:id="rId4" xr:uid="{E3440A7A-9DF5-4BD2-ABB1-AFF25B04F4AC}"/>
+    <hyperlink ref="Q3" r:id="rId5" xr:uid="{2C197A79-4E8D-4A85-A96C-97A0E1307524}"/>
+    <hyperlink ref="P4" r:id="rId6" xr:uid="{A67ED444-F017-41F1-8FCD-030E9CB2CED6}"/>
+    <hyperlink ref="Q4" r:id="rId7" xr:uid="{91F5747B-B161-47E0-A8CD-57C4EC6A89BA}"/>
+    <hyperlink ref="P5" r:id="rId8" xr:uid="{FB845758-F2B7-4FCB-B9C4-9D277957A9C2}"/>
+    <hyperlink ref="P6" r:id="rId9" xr:uid="{86DAB206-CE0A-452F-9861-95F49A78368A}"/>
+    <hyperlink ref="Q6" r:id="rId10" xr:uid="{6F5FA695-FD59-410E-9551-BDB0967C9BDB}"/>
+    <hyperlink ref="P7" r:id="rId11" xr:uid="{9E558C1F-9F50-4399-8E48-895D64753BB8}"/>
+    <hyperlink ref="P8" r:id="rId12" xr:uid="{CD4C5C91-1C21-4A19-A20C-3BA4AFA96220}"/>
+    <hyperlink ref="P9" r:id="rId13" xr:uid="{3106ED78-709C-4593-9CA3-060B12000B9F}"/>
+    <hyperlink ref="Q9" r:id="rId14" xr:uid="{B8BB7C6A-F612-4DD7-9842-68272B9974AD}"/>
+    <hyperlink ref="P10" r:id="rId15" xr:uid="{B859F619-414F-4EF9-8626-9F45BA0CEBB8}"/>
+    <hyperlink ref="Q10" r:id="rId16" xr:uid="{55685B34-15DA-4989-94D6-8C134922781E}"/>
+    <hyperlink ref="P11" r:id="rId17" xr:uid="{865402AF-1612-4FD1-89F5-9103C95E5141}"/>
+    <hyperlink ref="Q11" r:id="rId18" xr:uid="{7174D598-EC3F-483C-BDB8-869E0B8AF361}"/>
+    <hyperlink ref="P12" r:id="rId19" xr:uid="{8EB138DE-3548-4935-B8BA-A80F332C7547}"/>
+    <hyperlink ref="P13" r:id="rId20" xr:uid="{030979C6-729A-4CA8-9863-F034B29531B8}"/>
+    <hyperlink ref="P14" r:id="rId21" xr:uid="{E78B413F-4E33-4E43-BDE8-193FD47A4F40}"/>
+    <hyperlink ref="P16" r:id="rId22" xr:uid="{6E14F61A-3A44-46F4-A1EA-8D425ED4615E}"/>
+    <hyperlink ref="Q16" r:id="rId23" xr:uid="{6F3EDC96-F2AB-4C90-AAF5-A2A12B08768E}"/>
+    <hyperlink ref="P17" r:id="rId24" xr:uid="{AE4725A0-887A-46C6-99E7-958FE5BDCB0C}"/>
+    <hyperlink ref="Q17" r:id="rId25" xr:uid="{4D2F612B-1939-4980-8A2E-3270FE5C5409}"/>
+    <hyperlink ref="P18" r:id="rId26" xr:uid="{AE2C6CBC-91AE-44C0-BEAF-5B0B25CEEC7C}"/>
+    <hyperlink ref="Q18" r:id="rId27" xr:uid="{4AE79112-0011-41D4-ACF5-D4C1F8131FED}"/>
+    <hyperlink ref="P19" r:id="rId28" xr:uid="{154A5634-4EBA-4291-9D79-20044072C061}"/>
+    <hyperlink ref="P20" r:id="rId29" xr:uid="{B7265333-C422-41BB-8F01-A13EB946490A}"/>
+    <hyperlink ref="Q20" r:id="rId30" xr:uid="{E9056260-8DF8-48B1-AE3F-6FC0DFCAC1BA}"/>
+    <hyperlink ref="P21" r:id="rId31" xr:uid="{B5DAA74E-2CC7-4511-B54D-5C7787744C06}"/>
+    <hyperlink ref="P22" r:id="rId32" xr:uid="{9826A3E7-34D5-4B6D-8312-BB8F1CF8D9B1}"/>
+    <hyperlink ref="Q22" r:id="rId33" display="https://www.river.go.jp/kawabou/pc/tm?zm=12&amp;clat=34.60241096129153&amp;clon=135.76938629150393&amp;fld=0&amp;mapType=0&amp;viewGrpStg=0&amp;viewRd=1&amp;viewRW=1&amp;viewRl=1&amp;viewRn=1&amp;viewPoint=1&amp;ext=0&amp;itmkndCd=200&amp;scamId=107425042&amp;ownCd=7425&amp;sysCamId=7425042" xr:uid="{DA1DF261-6A32-429E-A114-E2B2F6548233}"/>
+    <hyperlink ref="P23" r:id="rId34" xr:uid="{232C94BD-E4E6-4EF8-AE62-28BD905E1A6C}"/>
+    <hyperlink ref="P24" r:id="rId35" xr:uid="{E3796CE5-9C4D-4BE3-A426-114230918EC8}"/>
+    <hyperlink ref="Q24" r:id="rId36" xr:uid="{1E40C976-7E5A-4740-BE13-5B483E23AD72}"/>
+    <hyperlink ref="P25" r:id="rId37" xr:uid="{BCA65EBC-E59E-49CA-864A-7EDC309DCBA0}"/>
+    <hyperlink ref="P26" r:id="rId38" xr:uid="{03B784DC-ABEB-4E38-B1D4-09A032EFB5F1}"/>
+    <hyperlink ref="P27" r:id="rId39" xr:uid="{761BC090-EC91-480E-A1DD-1AD3ADC583CF}"/>
+    <hyperlink ref="P28" r:id="rId40" xr:uid="{1D1FD9CF-3BF7-4F53-886F-EF8F770963C3}"/>
+    <hyperlink ref="Q28" r:id="rId41" xr:uid="{BC9B9A13-6428-4833-95E2-7DAD4AF55AD4}"/>
+    <hyperlink ref="P29" r:id="rId42" xr:uid="{BCD1C373-B69E-4366-B759-FE73F6C96251}"/>
+    <hyperlink ref="Q29" r:id="rId43" xr:uid="{C81E2CD2-DFA0-4F64-8373-112209FBDE4E}"/>
+    <hyperlink ref="P30" r:id="rId44" xr:uid="{33441477-EA47-4147-8361-D36451B51ADF}"/>
+    <hyperlink ref="P31" r:id="rId45" xr:uid="{60077CF3-A9E2-4AF4-9DC4-B8066C8AE43E}"/>
+    <hyperlink ref="P32" r:id="rId46" xr:uid="{4B33F0E6-8FC6-4531-877B-110204908392}"/>
+    <hyperlink ref="P33" r:id="rId47" xr:uid="{3AF0EBDD-6107-471E-BF9D-A8F62FD0E727}"/>
+    <hyperlink ref="Q33" r:id="rId48" xr:uid="{70F24105-5F61-4BA5-9D08-6A7F0A0C8BB4}"/>
+    <hyperlink ref="P34" r:id="rId49" xr:uid="{64CCD285-2A46-4D83-BB11-8B0ADE7C30BB}"/>
+    <hyperlink ref="Q34" r:id="rId50" xr:uid="{A6C9C94A-AE6B-4354-8159-84525A85A490}"/>
+    <hyperlink ref="P35" r:id="rId51" xr:uid="{7BFF2452-A754-4B8B-A2D9-8A9DF535A2E7}"/>
+    <hyperlink ref="Q35" r:id="rId52" xr:uid="{E831222A-9F5C-482A-9142-E0FB5BDBBF7D}"/>
+    <hyperlink ref="P36" r:id="rId53" xr:uid="{0EA32899-BE39-459F-A75F-19F2A2CACFBC}"/>
+    <hyperlink ref="P37" r:id="rId54" xr:uid="{7AA35659-E8FF-4AFC-B878-ADF477A380B7}"/>
+    <hyperlink ref="P38" r:id="rId55" xr:uid="{76AF3A8B-0A6B-4F0F-9147-F819C4161658}"/>
+    <hyperlink ref="P39" r:id="rId56" xr:uid="{DDAE6DE0-0B74-48B2-8BB5-5D092752F32D}"/>
+    <hyperlink ref="P40" r:id="rId57" xr:uid="{D7314B06-3C86-4473-8603-F94080C2AF3F}"/>
+    <hyperlink ref="P41" r:id="rId58" xr:uid="{91A5565A-5A71-4A32-99AF-2704D12340EE}"/>
+    <hyperlink ref="P42" r:id="rId59" xr:uid="{567BA0F0-BD1D-46CD-8516-2F0ACCD8D2B5}"/>
+    <hyperlink ref="Q42" r:id="rId60" xr:uid="{DD6A56A7-61D7-4C94-9E2D-D093294E8576}"/>
+    <hyperlink ref="P43" r:id="rId61" xr:uid="{F5EE3DE8-0194-4FF2-8B4B-E06078566D82}"/>
+    <hyperlink ref="P44" r:id="rId62" xr:uid="{7A139CC9-CC03-43B4-A26B-22132F2D00DD}"/>
+    <hyperlink ref="Q44" r:id="rId63" xr:uid="{219C3CF3-8803-4E1D-9F8C-54AD57B46C2E}"/>
+    <hyperlink ref="P45" r:id="rId64" xr:uid="{A93AD36D-52BE-48CF-8D41-48B09B834FB2}"/>
+    <hyperlink ref="Q45" r:id="rId65" xr:uid="{4F074575-4A63-4DA9-B682-95245C34D028}"/>
+    <hyperlink ref="Q46" r:id="rId66" xr:uid="{DEF28B44-B0DE-40EB-BC49-D84DF0889A84}"/>
+    <hyperlink ref="P46" r:id="rId67" xr:uid="{F46B48A4-C76F-4830-B8EC-AD38D7D38BD3}"/>
+    <hyperlink ref="P47" r:id="rId68" xr:uid="{A5078E1A-0274-4D2F-8205-356E668543A8}"/>
+    <hyperlink ref="P48" r:id="rId69" xr:uid="{299921A5-1E2D-4CC2-B084-3E4A1470A88D}"/>
+    <hyperlink ref="Q48" r:id="rId70" xr:uid="{1494FC1D-5B07-4ED2-9E2E-B26EAC276805}"/>
+    <hyperlink ref="P49" r:id="rId71" xr:uid="{D03F1817-E00E-4F69-AD8F-9C0EBBA8E8BC}"/>
+    <hyperlink ref="P50" r:id="rId72" xr:uid="{3069C10A-9C10-4333-886D-7E2DDE826DEE}"/>
+    <hyperlink ref="Q50" r:id="rId73" xr:uid="{AE733813-0DB9-4200-B20A-3376496AEB7F}"/>
+    <hyperlink ref="P51" r:id="rId74" xr:uid="{F2443606-D331-4786-BAC7-6896BFCECFF0}"/>
+    <hyperlink ref="Q51" r:id="rId75" xr:uid="{DC99C0E7-F0E5-4042-B048-3E31BD1DF48D}"/>
+    <hyperlink ref="P52" r:id="rId76" xr:uid="{624C851A-6C89-4CC0-A219-B18F3A06C35A}"/>
+    <hyperlink ref="Q52" r:id="rId77" xr:uid="{EFE49E4B-7BEC-4B89-A015-D646BA9B9951}"/>
+    <hyperlink ref="P53" r:id="rId78" xr:uid="{91E4958D-9FED-453C-9238-7A0EBF24DDA0}"/>
+    <hyperlink ref="Q53" r:id="rId79" xr:uid="{5DDD53DC-F31C-4321-BE2C-81076DE0B813}"/>
+    <hyperlink ref="P54" r:id="rId80" xr:uid="{BD6CEAB1-F5BF-48EB-B476-B1CA03B6792C}"/>
+    <hyperlink ref="Q54" r:id="rId81" xr:uid="{637C6B19-6DA4-42D4-A59A-962FAB655863}"/>
+    <hyperlink ref="P55" r:id="rId82" xr:uid="{37F4E260-CCBC-4790-A8E6-366E907778D3}"/>
+    <hyperlink ref="P56" r:id="rId83" xr:uid="{50728D18-80A2-41C9-9684-71EA672643A9}"/>
+    <hyperlink ref="P57" r:id="rId84" xr:uid="{84506F98-72FF-479B-8A89-5F966E562F30}"/>
+    <hyperlink ref="Q58" r:id="rId85" xr:uid="{A86E6E98-036A-4DF0-9ED2-826A0909C637}"/>
+    <hyperlink ref="Q56" r:id="rId86" xr:uid="{591132DA-6FDD-46B8-9B34-50E4B30C2326}"/>
+    <hyperlink ref="P58" r:id="rId87" xr:uid="{0362DE56-C757-49DA-A2CA-955756DD3CCA}"/>
+    <hyperlink ref="Q59" r:id="rId88" xr:uid="{6BF187E7-C20D-4B10-AA4F-FA6075A39F95}"/>
+    <hyperlink ref="P59" r:id="rId89" xr:uid="{11EE20EB-F8A8-4D0A-81AB-7B63150DF82B}"/>
+    <hyperlink ref="P60" r:id="rId90" xr:uid="{01A3C01F-4051-4E83-9E5A-1E98B5CA9CC7}"/>
+    <hyperlink ref="Q60" r:id="rId91" xr:uid="{24C3792C-A3AE-4FC5-9109-1C2FD4D09EB0}"/>
+    <hyperlink ref="P62" r:id="rId92" xr:uid="{6B9D1916-F27D-4F02-8A42-18975E2E36EA}"/>
+    <hyperlink ref="Q62" r:id="rId93" xr:uid="{071CEDC8-7D72-4C11-9945-DED6C41A8B1E}"/>
+    <hyperlink ref="P63" r:id="rId94" xr:uid="{0B03128E-2C50-4B1D-B2DE-77E1B45714F3}"/>
+    <hyperlink ref="P61" r:id="rId95" xr:uid="{E5EE7183-E9F5-457B-A884-E40763AC314A}"/>
+    <hyperlink ref="P64" r:id="rId96" xr:uid="{8C44961E-4772-465F-A837-8EA48FA3CEA6}"/>
+    <hyperlink ref="P65" r:id="rId97" xr:uid="{E937E12F-2628-45E0-8260-0E703214499D}"/>
+    <hyperlink ref="Q65" r:id="rId98" xr:uid="{5E41DCA2-3AED-46D9-BC02-3E082D847A97}"/>
+    <hyperlink ref="P66" r:id="rId99" xr:uid="{67003E07-4EED-4ADA-8325-2F767337709A}"/>
+    <hyperlink ref="P71" r:id="rId100" xr:uid="{8826EBFB-91BB-443B-896A-E284D64A6E0A}"/>
+    <hyperlink ref="P67" r:id="rId101" xr:uid="{C54722E9-BD3E-4C18-953D-D1515B485902}"/>
+    <hyperlink ref="P68" r:id="rId102" xr:uid="{B907FE13-5849-4C10-AE8D-B2FE098659CE}"/>
+    <hyperlink ref="P69" r:id="rId103" xr:uid="{9B4FE783-ECE6-4692-AAD8-93605DF44DF4}"/>
+    <hyperlink ref="P70" r:id="rId104" xr:uid="{948B94EE-FB54-44C6-B50E-2DA23BB32796}"/>
+    <hyperlink ref="P72" r:id="rId105" xr:uid="{A411935B-1994-4049-8FF0-28FB42096408}"/>
+    <hyperlink ref="Q72" r:id="rId106" xr:uid="{2A76E0A4-EC10-4967-84E2-00BED5D358B3}"/>
+    <hyperlink ref="P73" r:id="rId107" xr:uid="{8EA3C855-2234-4C55-B597-13F9400E0BD0}"/>
+    <hyperlink ref="P74" r:id="rId108" xr:uid="{C4D2A0FA-2525-4F04-AEA8-7AB6E72B8789}"/>
+    <hyperlink ref="P75" r:id="rId109" xr:uid="{0D5A9C33-8FE8-403D-84EB-16AA4CB4AE04}"/>
+    <hyperlink ref="P76" r:id="rId110" xr:uid="{E01CEFD8-9FEC-4146-8A24-40D28CEFF048}"/>
+    <hyperlink ref="Q15" r:id="rId111" xr:uid="{5B72FD30-5AC0-4947-B9E9-5D1E55ECFC1C}"/>
+    <hyperlink ref="Q25" r:id="rId112" xr:uid="{1F40BFD5-1664-4B8E-9AD0-04899D1DF1D1}"/>
+    <hyperlink ref="Q23" r:id="rId113" xr:uid="{EA4009B5-D4FF-46BE-962D-5307A513DFE2}"/>
+    <hyperlink ref="Q30" r:id="rId114" xr:uid="{4C90473C-163E-4562-BED7-C580B121271C}"/>
+    <hyperlink ref="Q32" r:id="rId115" xr:uid="{476D1F67-6A1A-41C9-A843-3B3FC63DE9A7}"/>
+    <hyperlink ref="Q38" r:id="rId116" xr:uid="{8F7D7FA1-3D5E-4BF5-92E2-A491876D2137}"/>
+    <hyperlink ref="Q43" r:id="rId117" xr:uid="{F9E60127-FA03-468B-A56D-60844C91CFF6}"/>
+    <hyperlink ref="Q47" r:id="rId118" xr:uid="{F0FB7F74-3E66-47AE-B1A1-1401657ACFCA}"/>
+    <hyperlink ref="Q70" r:id="rId119" xr:uid="{E5C917D2-559D-41F8-A179-79AEF2730A64}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
